--- a/Plantilla desde 0.xlsx
+++ b/Plantilla desde 0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pablo.Garcia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AD33663-C04D-4EC8-B831-08A6415F6DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FC77E9-7A4B-403F-AE83-C88646F72431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,7 +242,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="48">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -457,56 +492,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D43C936F-5C1F-4D66-B347-FAF56D52F3D3}" name="Table1" displayName="Table1" ref="A1:AK2" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D43C936F-5C1F-4D66-B347-FAF56D52F3D3}" name="Table1" displayName="Table1" ref="A1:AK2" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:AK2" xr:uid="{D43C936F-5C1F-4D66-B347-FAF56D52F3D3}"/>
   <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{F2634B9C-D13D-4E26-A3FA-234BA6237C2F}" name="Empleado" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{31FF678E-2FB0-4C5F-8D72-D4276336A3B4}" name="Acumulados _x000a_Visperas" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{5FBF903D-BF42-4D63-AD9C-A458EB226E95}" name="Acumulados _x000a_Festivos" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{917696FA-3F3E-4B95-A881-9D9C8243A0CE}" name="Objetivo total" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{5DA48378-63EE-4A68-B890-FE7C9D6AA64F}" name="Objetivo _x000a_Visperas (mes actual)" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{FD964CD3-852A-45BE-8F8B-4B119E7DBDF8}" name="Objetivo_x000a_ Festivo (mes actual)" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{29EDB536-2866-4DDD-9755-10EB96D12E17}" name="1" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{9F1F15CE-46B0-4D72-A9C4-D03353D7E534}" name="2" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{40D6323D-3833-447B-9AFC-481173674ECC}" name="3" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{5A3B56F5-CD81-4240-88E8-6FC4928DBB56}" name="4" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{826AAB5F-6F9E-4350-A0A7-1638EDA2F6FA}" name="5" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{F8339E87-2BB4-4B92-A2D1-804498FFEAE0}" name="6" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{E1BF1EBE-F7D4-4703-B7CD-4E49F482A834}" name="7" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{87A57E40-2A44-448E-96F8-BF27520D2705}" name="8" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{1D71D0C2-5A99-44C5-BDBE-9B07C2762E32}" name="9" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{F1A3E41F-6B99-443D-849E-1CDBB9A51972}" name="10" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{C084DE24-9AEC-4152-B1EB-3220EC16D318}" name="11" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{909736DB-79FF-4C28-8560-65E1A282C295}" name="12" dataDxfId="25"/>
-    <tableColumn id="21" xr3:uid="{49723E9D-AAF7-44D0-8F0C-7B5531373BC4}" name="13" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{816E6B1C-3DDA-43AB-A3C0-EAB00E05055D}" name="14" dataDxfId="23"/>
-    <tableColumn id="23" xr3:uid="{334972B4-3628-4957-8C22-0288FA44BF3E}" name="15" dataDxfId="22"/>
-    <tableColumn id="24" xr3:uid="{8FDA928E-762A-49CF-8EC2-E6AF0199711F}" name="16" dataDxfId="21"/>
-    <tableColumn id="25" xr3:uid="{72EA7B5D-FF6B-4FDC-BACD-3F6FFEA51852}" name="17" dataDxfId="20"/>
-    <tableColumn id="26" xr3:uid="{27DD8073-3837-4916-93D0-DC36E9F64EC5}" name="18" dataDxfId="19"/>
-    <tableColumn id="27" xr3:uid="{CBE3670C-101C-49A6-A709-7850EC3DFBB3}" name="19" dataDxfId="18"/>
-    <tableColumn id="28" xr3:uid="{2794A886-93B6-44A2-B650-3607E39E392B}" name="20" dataDxfId="17"/>
-    <tableColumn id="29" xr3:uid="{AD733172-1EFC-4E44-BBCA-B253057F98F4}" name="21" dataDxfId="16"/>
-    <tableColumn id="30" xr3:uid="{C1554603-5D86-48D9-9AAA-6002C1985AC0}" name="22" dataDxfId="15"/>
-    <tableColumn id="31" xr3:uid="{8FC750E3-6040-41C6-B0FE-5D706E949F3C}" name="23" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{AD15D69D-FACF-4B24-BB62-0A588ADACF52}" name="24" dataDxfId="13"/>
-    <tableColumn id="33" xr3:uid="{EFD7E76A-CBF4-4DDD-9E5D-EA47FB33F0D4}" name="25" dataDxfId="12"/>
-    <tableColumn id="34" xr3:uid="{D28C0A98-5D6C-4EAE-8B10-3D0AA173085B}" name="26" dataDxfId="11"/>
-    <tableColumn id="35" xr3:uid="{A69D3B14-9FD4-4038-8D80-43275163A021}" name="27" dataDxfId="10"/>
-    <tableColumn id="36" xr3:uid="{336D34F9-B8C4-4652-8F8B-96787306AEE0}" name="28" dataDxfId="9"/>
-    <tableColumn id="37" xr3:uid="{578DD076-3809-4A14-9C79-51CFABCE45E8}" name="29" dataDxfId="8"/>
-    <tableColumn id="38" xr3:uid="{E26974DF-535D-423D-8646-94ABB3384986}" name="30" dataDxfId="7"/>
-    <tableColumn id="39" xr3:uid="{7E52291C-D5AA-4F6D-A85E-31C7B53AD83A}" name="31" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{F2634B9C-D13D-4E26-A3FA-234BA6237C2F}" name="Empleado" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{31FF678E-2FB0-4C5F-8D72-D4276336A3B4}" name="Acumulados _x000a_Visperas" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{5FBF903D-BF42-4D63-AD9C-A458EB226E95}" name="Acumulados _x000a_Festivos" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{917696FA-3F3E-4B95-A881-9D9C8243A0CE}" name="Objetivo total" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{5DA48378-63EE-4A68-B890-FE7C9D6AA64F}" name="Objetivo _x000a_Visperas (mes actual)" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{FD964CD3-852A-45BE-8F8B-4B119E7DBDF8}" name="Objetivo_x000a_ Festivo (mes actual)" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{29EDB536-2866-4DDD-9755-10EB96D12E17}" name="1" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{9F1F15CE-46B0-4D72-A9C4-D03353D7E534}" name="2" dataDxfId="38"/>
+    <tableColumn id="11" xr3:uid="{40D6323D-3833-447B-9AFC-481173674ECC}" name="3" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{5A3B56F5-CD81-4240-88E8-6FC4928DBB56}" name="4" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{826AAB5F-6F9E-4350-A0A7-1638EDA2F6FA}" name="5" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{F8339E87-2BB4-4B92-A2D1-804498FFEAE0}" name="6" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{E1BF1EBE-F7D4-4703-B7CD-4E49F482A834}" name="7" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{87A57E40-2A44-448E-96F8-BF27520D2705}" name="8" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{1D71D0C2-5A99-44C5-BDBE-9B07C2762E32}" name="9" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{F1A3E41F-6B99-443D-849E-1CDBB9A51972}" name="10" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{C084DE24-9AEC-4152-B1EB-3220EC16D318}" name="11" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{909736DB-79FF-4C28-8560-65E1A282C295}" name="12" dataDxfId="28"/>
+    <tableColumn id="21" xr3:uid="{49723E9D-AAF7-44D0-8F0C-7B5531373BC4}" name="13" dataDxfId="27"/>
+    <tableColumn id="22" xr3:uid="{816E6B1C-3DDA-43AB-A3C0-EAB00E05055D}" name="14" dataDxfId="26"/>
+    <tableColumn id="23" xr3:uid="{334972B4-3628-4957-8C22-0288FA44BF3E}" name="15" dataDxfId="25"/>
+    <tableColumn id="24" xr3:uid="{8FDA928E-762A-49CF-8EC2-E6AF0199711F}" name="16" dataDxfId="24"/>
+    <tableColumn id="25" xr3:uid="{72EA7B5D-FF6B-4FDC-BACD-3F6FFEA51852}" name="17" dataDxfId="23"/>
+    <tableColumn id="26" xr3:uid="{27DD8073-3837-4916-93D0-DC36E9F64EC5}" name="18" dataDxfId="22"/>
+    <tableColumn id="27" xr3:uid="{CBE3670C-101C-49A6-A709-7850EC3DFBB3}" name="19" dataDxfId="21"/>
+    <tableColumn id="28" xr3:uid="{2794A886-93B6-44A2-B650-3607E39E392B}" name="20" dataDxfId="20"/>
+    <tableColumn id="29" xr3:uid="{AD733172-1EFC-4E44-BBCA-B253057F98F4}" name="21" dataDxfId="19"/>
+    <tableColumn id="30" xr3:uid="{C1554603-5D86-48D9-9AAA-6002C1985AC0}" name="22" dataDxfId="18"/>
+    <tableColumn id="31" xr3:uid="{8FC750E3-6040-41C6-B0FE-5D706E949F3C}" name="23" dataDxfId="17"/>
+    <tableColumn id="32" xr3:uid="{AD15D69D-FACF-4B24-BB62-0A588ADACF52}" name="24" dataDxfId="16"/>
+    <tableColumn id="33" xr3:uid="{EFD7E76A-CBF4-4DDD-9E5D-EA47FB33F0D4}" name="25" dataDxfId="15"/>
+    <tableColumn id="34" xr3:uid="{D28C0A98-5D6C-4EAE-8B10-3D0AA173085B}" name="26" dataDxfId="14"/>
+    <tableColumn id="35" xr3:uid="{A69D3B14-9FD4-4038-8D80-43275163A021}" name="27" dataDxfId="13"/>
+    <tableColumn id="36" xr3:uid="{336D34F9-B8C4-4652-8F8B-96787306AEE0}" name="28" dataDxfId="12"/>
+    <tableColumn id="37" xr3:uid="{578DD076-3809-4A14-9C79-51CFABCE45E8}" name="29" dataDxfId="11"/>
+    <tableColumn id="38" xr3:uid="{E26974DF-535D-423D-8646-94ABB3384986}" name="30" dataDxfId="10"/>
+    <tableColumn id="39" xr3:uid="{7E52291C-D5AA-4F6D-A85E-31C7B53AD83A}" name="31" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{21B349EE-483F-4C7A-A7EC-6C23BED7C53F}" name="Table2" displayName="Table2" ref="A1:A5" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{21B349EE-483F-4C7A-A7EC-6C23BED7C53F}" name="Table2" displayName="Table2" ref="A1:A5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:A5" xr:uid="{21B349EE-483F-4C7A-A7EC-6C23BED7C53F}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{48027637-DBCA-402B-922B-81BAE322E440}" name="Column1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{48027637-DBCA-402B-922B-81BAE322E440}" name="Column1" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -846,9 +881,7 @@
     <col min="6" max="6" width="22.5" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="15" width="3.75" style="8" customWidth="1"/>
     <col min="16" max="37" width="4.75" style="8" customWidth="1"/>
-    <col min="38" max="38" width="9" style="8"/>
-    <col min="39" max="39" width="9.875" style="8" customWidth="1"/>
-    <col min="40" max="16384" width="9" style="8"/>
+    <col min="38" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -1005,7 +1038,7 @@
     </row>
   </sheetData>
   <sheetProtection insertRows="0" deleteRows="0" selectLockedCells="1" sort="0"/>
-  <conditionalFormatting sqref="G2:AK2">
+  <conditionalFormatting sqref="G2:AK25">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"G"</formula>
     </cfRule>
